--- a/artfynd/A 22195-2025 artfynd.xlsx
+++ b/artfynd/A 22195-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127713720</v>
       </c>
       <c r="B2" t="n">
-        <v>56853</v>
+        <v>56855</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -791,7 +791,7 @@
         <v>127713673</v>
       </c>
       <c r="B3" t="n">
-        <v>57658</v>
+        <v>57660</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -904,7 +904,7 @@
         <v>127713619</v>
       </c>
       <c r="B4" t="n">
-        <v>57821</v>
+        <v>57823</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1017,7 +1017,7 @@
         <v>127713652</v>
       </c>
       <c r="B5" t="n">
-        <v>57819</v>
+        <v>57821</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 22195-2025 artfynd.xlsx
+++ b/artfynd/A 22195-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127713720</v>
       </c>
       <c r="B2" t="n">
-        <v>56855</v>
+        <v>56858</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -791,7 +791,7 @@
         <v>127713673</v>
       </c>
       <c r="B3" t="n">
-        <v>57660</v>
+        <v>57663</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -904,7 +904,7 @@
         <v>127713619</v>
       </c>
       <c r="B4" t="n">
-        <v>57823</v>
+        <v>57826</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1017,7 +1017,7 @@
         <v>127713652</v>
       </c>
       <c r="B5" t="n">
-        <v>57821</v>
+        <v>57824</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 22195-2025 artfynd.xlsx
+++ b/artfynd/A 22195-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127713720</v>
       </c>
       <c r="B2" t="n">
-        <v>56858</v>
+        <v>56864</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -791,7 +791,7 @@
         <v>127713673</v>
       </c>
       <c r="B3" t="n">
-        <v>57663</v>
+        <v>57669</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -904,7 +904,7 @@
         <v>127713619</v>
       </c>
       <c r="B4" t="n">
-        <v>57826</v>
+        <v>57832</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1017,7 +1017,7 @@
         <v>127713652</v>
       </c>
       <c r="B5" t="n">
-        <v>57824</v>
+        <v>57830</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 22195-2025 artfynd.xlsx
+++ b/artfynd/A 22195-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1125,6 +1125,129 @@
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>128223586</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57669</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Motti-Lasses myr, Dlr</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>485874</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6666279</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Egil Borgne</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Egil Borgne</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 22195-2025 artfynd.xlsx
+++ b/artfynd/A 22195-2025 artfynd.xlsx
@@ -791,7 +791,7 @@
         <v>127713673</v>
       </c>
       <c r="B3" t="n">
-        <v>57669</v>
+        <v>57670</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -904,7 +904,7 @@
         <v>127713619</v>
       </c>
       <c r="B4" t="n">
-        <v>57832</v>
+        <v>57833</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1017,7 +1017,7 @@
         <v>127713652</v>
       </c>
       <c r="B5" t="n">
-        <v>57830</v>
+        <v>57831</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1130,7 +1130,7 @@
         <v>128223586</v>
       </c>
       <c r="B6" t="n">
-        <v>57669</v>
+        <v>57670</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 22195-2025 artfynd.xlsx
+++ b/artfynd/A 22195-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127713720</v>
       </c>
       <c r="B2" t="n">
-        <v>56864</v>
+        <v>56875</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -791,7 +791,7 @@
         <v>127713673</v>
       </c>
       <c r="B3" t="n">
-        <v>57670</v>
+        <v>57681</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -904,7 +904,7 @@
         <v>127713619</v>
       </c>
       <c r="B4" t="n">
-        <v>57833</v>
+        <v>57844</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1017,7 +1017,7 @@
         <v>127713652</v>
       </c>
       <c r="B5" t="n">
-        <v>57831</v>
+        <v>57842</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1130,7 +1130,7 @@
         <v>128223586</v>
       </c>
       <c r="B6" t="n">
-        <v>57670</v>
+        <v>57682</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 22195-2025 artfynd.xlsx
+++ b/artfynd/A 22195-2025 artfynd.xlsx
@@ -1130,7 +1130,7 @@
         <v>128223586</v>
       </c>
       <c r="B6" t="n">
-        <v>57682</v>
+        <v>57686</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 22195-2025 artfynd.xlsx
+++ b/artfynd/A 22195-2025 artfynd.xlsx
@@ -1130,7 +1130,7 @@
         <v>128223586</v>
       </c>
       <c r="B6" t="n">
-        <v>57686</v>
+        <v>57713</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 22195-2025 artfynd.xlsx
+++ b/artfynd/A 22195-2025 artfynd.xlsx
@@ -1253,7 +1253,7 @@
         <v>131255264</v>
       </c>
       <c r="B7" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 22195-2025 artfynd.xlsx
+++ b/artfynd/A 22195-2025 artfynd.xlsx
@@ -1253,7 +1253,7 @@
         <v>131255264</v>
       </c>
       <c r="B7" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1360,7 +1360,7 @@
         <v>131255137</v>
       </c>
       <c r="B8" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1477,7 +1477,7 @@
         <v>131302285</v>
       </c>
       <c r="B9" t="n">
-        <v>57881</v>
+        <v>57883</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 22195-2025 artfynd.xlsx
+++ b/artfynd/A 22195-2025 artfynd.xlsx
@@ -1253,7 +1253,7 @@
         <v>131255264</v>
       </c>
       <c r="B7" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1360,7 +1360,7 @@
         <v>131255137</v>
       </c>
       <c r="B8" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1477,7 +1477,7 @@
         <v>131302285</v>
       </c>
       <c r="B9" t="n">
-        <v>57883</v>
+        <v>57884</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 22195-2025 artfynd.xlsx
+++ b/artfynd/A 22195-2025 artfynd.xlsx
@@ -1253,7 +1253,7 @@
         <v>131255264</v>
       </c>
       <c r="B7" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1360,7 +1360,7 @@
         <v>131255137</v>
       </c>
       <c r="B8" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1477,7 +1477,7 @@
         <v>131302285</v>
       </c>
       <c r="B9" t="n">
-        <v>57884</v>
+        <v>57885</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 22195-2025 artfynd.xlsx
+++ b/artfynd/A 22195-2025 artfynd.xlsx
@@ -1253,7 +1253,7 @@
         <v>131255264</v>
       </c>
       <c r="B7" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1360,7 +1360,7 @@
         <v>131255137</v>
       </c>
       <c r="B8" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1477,7 +1477,7 @@
         <v>131302285</v>
       </c>
       <c r="B9" t="n">
-        <v>57885</v>
+        <v>57888</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 22195-2025 artfynd.xlsx
+++ b/artfynd/A 22195-2025 artfynd.xlsx
@@ -1253,7 +1253,7 @@
         <v>131255264</v>
       </c>
       <c r="B7" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1360,7 +1360,7 @@
         <v>131255137</v>
       </c>
       <c r="B8" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1477,7 +1477,7 @@
         <v>131302285</v>
       </c>
       <c r="B9" t="n">
-        <v>57888</v>
+        <v>57889</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 22195-2025 artfynd.xlsx
+++ b/artfynd/A 22195-2025 artfynd.xlsx
@@ -1253,7 +1253,7 @@
         <v>131255264</v>
       </c>
       <c r="B7" t="n">
-        <v>79254</v>
+        <v>79260</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1360,7 +1360,7 @@
         <v>131255137</v>
       </c>
       <c r="B8" t="n">
-        <v>57892</v>
+        <v>57898</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1477,7 +1477,7 @@
         <v>131302285</v>
       </c>
       <c r="B9" t="n">
-        <v>57889</v>
+        <v>57895</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 22195-2025 artfynd.xlsx
+++ b/artfynd/A 22195-2025 artfynd.xlsx
@@ -1253,7 +1253,7 @@
         <v>131255264</v>
       </c>
       <c r="B7" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1360,7 +1360,7 @@
         <v>131255137</v>
       </c>
       <c r="B8" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1477,7 +1477,7 @@
         <v>131302285</v>
       </c>
       <c r="B9" t="n">
-        <v>57895</v>
+        <v>57896</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 22195-2025 artfynd.xlsx
+++ b/artfynd/A 22195-2025 artfynd.xlsx
@@ -1253,7 +1253,7 @@
         <v>131255264</v>
       </c>
       <c r="B7" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1360,7 +1360,7 @@
         <v>131255137</v>
       </c>
       <c r="B8" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1477,7 +1477,7 @@
         <v>131302285</v>
       </c>
       <c r="B9" t="n">
-        <v>57896</v>
+        <v>57899</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 22195-2025 artfynd.xlsx
+++ b/artfynd/A 22195-2025 artfynd.xlsx
@@ -1477,7 +1477,7 @@
         <v>131302285</v>
       </c>
       <c r="B9" t="n">
-        <v>57899</v>
+        <v>57901</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 22195-2025 artfynd.xlsx
+++ b/artfynd/A 22195-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,61 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127713720</v>
+        <v>131255264</v>
       </c>
       <c r="B2" t="n">
-        <v>56875</v>
+        <v>79327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Stora vittjärn, Dlr</t>
+          <t>Stora Vittjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>485846</v>
+        <v>485818</v>
       </c>
       <c r="R2" t="n">
-        <v>6666209</v>
+        <v>6666268</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -756,12 +740,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2026-02-22</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>09:18</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2026-02-22</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>09:18</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -776,12 +770,12 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Egil Borgne</t>
+          <t>Tobias Hellberg</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Egil Borgne</t>
+          <t>Tobias Hellberg</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -791,11 +785,11 @@
         <v>127713673</v>
       </c>
       <c r="B3" t="n">
-        <v>57681</v>
+        <v>57950</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -901,32 +895,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127713619</v>
+        <v>128223586</v>
       </c>
       <c r="B4" t="n">
-        <v>57844</v>
+        <v>57950</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -936,7 +930,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>pulli</t>
+          <t>adult</t>
         </is>
       </c>
       <c r="L4" t="inlineStr"/>
@@ -948,14 +942,14 @@
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Stora vittjärn, Dlr</t>
+          <t>Motti-Lasses myr, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>485846</v>
+        <v>485874</v>
       </c>
       <c r="R4" t="n">
-        <v>6666209</v>
+        <v>6666279</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -982,12 +976,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-08-11</t>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>08:20</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-08-11</t>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>08:20</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1014,27 +1018,27 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127713652</v>
+        <v>131302285</v>
       </c>
       <c r="B5" t="n">
-        <v>57842</v>
+        <v>57950</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103020</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1042,33 +1046,25 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Stora vittjärn, Dlr</t>
+          <t>Död ved, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>485846</v>
+        <v>485798</v>
       </c>
       <c r="R5" t="n">
-        <v>6666209</v>
+        <v>6666146</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1095,12 +1091,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-08-11</t>
+          <t>2025-08-19</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-08-11</t>
+          <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Färska födosökningsspår av spillkråka på låga.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1127,10 +1128,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128223586</v>
+        <v>131255137</v>
       </c>
       <c r="B6" t="n">
-        <v>57713</v>
+        <v>57953</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1138,16 +1139,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1155,33 +1156,22 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Motti-Lasses myr, Dlr</t>
+          <t>Stora Vittjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>485874</v>
+        <v>485867</v>
       </c>
       <c r="R6" t="n">
-        <v>6666279</v>
+        <v>6666265</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1208,22 +1198,27 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-08-30</t>
+          <t>2026-02-22</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-08-30</t>
+          <t>2026-02-22</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:12</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1238,57 +1233,73 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Egil Borgne</t>
+          <t>Tobias Hellberg</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Egil Borgne</t>
+          <t>Tobias Hellberg</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131255264</v>
+        <v>127713720</v>
       </c>
       <c r="B7" t="n">
-        <v>79264</v>
+        <v>57141</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Stora Vittjärnen, Dlr</t>
+          <t>Stora vittjärn, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>485818</v>
+        <v>485846</v>
       </c>
       <c r="R7" t="n">
-        <v>6666268</v>
+        <v>6666209</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1315,22 +1326,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-02-22</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>09:18</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-02-22</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>09:18</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1345,22 +1346,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Tobias Hellberg</t>
+          <t>Egil Borgne</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Tobias Hellberg</t>
+          <t>Egil Borgne</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131255137</v>
+        <v>127713652</v>
       </c>
       <c r="B8" t="n">
-        <v>57902</v>
+        <v>58112</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1368,16 +1369,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>103020</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1385,22 +1386,33 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Stora Vittjärnen, Dlr</t>
+          <t>Stora vittjärn, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>485867</v>
+        <v>485846</v>
       </c>
       <c r="R8" t="n">
-        <v>6666265</v>
+        <v>6666209</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1427,27 +1439,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-02-22</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>09:12</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-02-22</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>09:12</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på gran</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1462,22 +1459,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Tobias Hellberg</t>
+          <t>Egil Borgne</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Tobias Hellberg</t>
+          <t>Egil Borgne</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131302285</v>
+        <v>127713619</v>
       </c>
       <c r="B9" t="n">
-        <v>57901</v>
+        <v>58114</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1485,42 +1482,50 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>pulli</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Död ved, Dlr</t>
+          <t>Stora vittjärn, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>485798</v>
+        <v>485846</v>
       </c>
       <c r="R9" t="n">
-        <v>6666146</v>
+        <v>6666209</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1547,17 +1552,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-08-19</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-08-19</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Färska födosökningsspår av spillkråka på låga.</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1581,6 +1581,129 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>131302310</v>
+      </c>
+      <c r="B10" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Hällmark Stora vittjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>485738</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6666185</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-02-21</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-02-21</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Egil Borgne</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Egil Borgne</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
